--- a/src/main/resources/Errors.xlsx
+++ b/src/main/resources/Errors.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\REI_Automation_Project\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93C90EE-A07D-4129-99BD-56B9035737DB}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5AB47A1-360D-4AAD-990C-A3D40A97267F}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" activeTab="2" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" activeTab="4" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
   </bookViews>
   <sheets>
     <sheet name="AnnualError" sheetId="2" r:id="rId1"/>
     <sheet name="BI-MonthlyError" sheetId="3" r:id="rId2"/>
     <sheet name="MonthlyError" sheetId="4" r:id="rId3"/>
+    <sheet name="SemiAnnuallyError" sheetId="5" r:id="rId4"/>
+    <sheet name="Bi-MonthlyForEightRecord" sheetId="7" r:id="rId5"/>
+    <sheet name="NoScheduleStartDateError" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="18">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -80,6 +83,12 @@
   </si>
   <si>
     <t>Monthly</t>
+  </si>
+  <si>
+    <t>Semi-Annually</t>
+  </si>
+  <si>
+    <t>Calendar</t>
   </si>
 </sst>
 </file>
@@ -703,4 +712,270 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{217E2F9E-9199-408F-BE46-44297F0B7560}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="29.53515625" customWidth="1"/>
+    <col min="2" max="2" width="18.3828125" customWidth="1"/>
+    <col min="3" max="3" width="31.69140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71D36EAF-2C5D-489B-9FA4-63FF8286B375}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="26.69140625" customWidth="1"/>
+    <col min="2" max="2" width="25.61328125" customWidth="1"/>
+    <col min="3" max="3" width="30.69140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>455</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC3FD18-621C-4EB5-A9A2-608B2593CE23}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="27.07421875" customWidth="1"/>
+    <col min="2" max="2" width="24.23046875" customWidth="1"/>
+    <col min="3" max="3" width="27.3828125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/Errors.xlsx
+++ b/src/main/resources/Errors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\REI_Automation_Project\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Automation_Product\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5AB47A1-360D-4AAD-990C-A3D40A97267F}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13D902B-9B21-45BE-97F0-876BF4EB9E07}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" activeTab="4" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="6" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
   </bookViews>
   <sheets>
     <sheet name="AnnualError" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,9 @@
     <sheet name="MonthlyError" sheetId="4" r:id="rId3"/>
     <sheet name="SemiAnnuallyError" sheetId="5" r:id="rId4"/>
     <sheet name="Bi-MonthlyForEightRecord" sheetId="7" r:id="rId5"/>
-    <sheet name="NoScheduleStartDateError" sheetId="6" r:id="rId6"/>
+    <sheet name="Grant_Creation _Error" sheetId="8" r:id="rId6"/>
+    <sheet name="Grant_Creation _Error2" sheetId="9" r:id="rId7"/>
+    <sheet name="NoScheduleStartDateError" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="32">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -89,19 +91,67 @@
   </si>
   <si>
     <t>Calendar</t>
+  </si>
+  <si>
+    <t>ProjectTitle__c</t>
+  </si>
+  <si>
+    <t>Automation Execution Award</t>
+  </si>
+  <si>
+    <t>GrantAbbreviation__c</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>ProjectPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>BudgetCategoryPackage__c</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>fieldInternalOrganization__c</t>
+  </si>
+  <si>
+    <t>SAN DIEGO ELECTRICAL TRAINING TRUST</t>
+  </si>
+  <si>
+    <t>Program__c</t>
+  </si>
+  <si>
+    <t>Automation Permanent Internal Program</t>
+  </si>
+  <si>
+    <t>ExternalOrganization__c</t>
+  </si>
+  <si>
+    <t>Test Automation Organization</t>
+  </si>
+  <si>
+    <t>ProjectPeriodStartDate__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -124,8 +174,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -441,14 +498,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A3F775-4EF9-4E52-8B04-750C37159D13}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.765625" customWidth="1"/>
-    <col min="2" max="2" width="21.07421875" customWidth="1"/>
-    <col min="3" max="3" width="27.84375" customWidth="1"/>
+    <col min="1" max="1" width="17.7265625" customWidth="1"/>
+    <col min="2" max="2" width="21.08984375" customWidth="1"/>
+    <col min="3" max="3" width="27.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -459,7 +516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -470,7 +527,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -481,7 +538,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -492,7 +549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -503,7 +560,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -514,7 +571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -533,14 +590,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E04EE11-11AC-4EDB-8021-AA7ECF589184}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.61328125" customWidth="1"/>
+    <col min="1" max="1" width="20.6328125" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="24.765625" customWidth="1"/>
+    <col min="3" max="3" width="24.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -551,7 +608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -562,7 +619,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -573,7 +630,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -584,7 +641,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -595,7 +652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -606,7 +663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -625,14 +682,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD01CD2B-7253-4FAA-9A4D-E901801ECEA6}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.61328125" customWidth="1"/>
-    <col min="2" max="2" width="21.3828125" customWidth="1"/>
-    <col min="3" max="3" width="22.4609375" customWidth="1"/>
+    <col min="1" max="1" width="18.6328125" customWidth="1"/>
+    <col min="2" max="2" width="21.36328125" customWidth="1"/>
+    <col min="3" max="3" width="22.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -643,7 +700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -654,7 +711,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -665,7 +722,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -676,7 +733,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -687,7 +744,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -698,7 +755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -717,14 +774,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{217E2F9E-9199-408F-BE46-44297F0B7560}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.53515625" customWidth="1"/>
-    <col min="2" max="2" width="18.3828125" customWidth="1"/>
-    <col min="3" max="3" width="31.69140625" customWidth="1"/>
+    <col min="1" max="1" width="29.54296875" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" customWidth="1"/>
+    <col min="3" max="3" width="31.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -735,7 +792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -746,7 +803,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -757,7 +814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -768,7 +825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -779,7 +836,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -790,7 +847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -810,14 +867,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71D36EAF-2C5D-489B-9FA4-63FF8286B375}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.69140625" customWidth="1"/>
-    <col min="2" max="2" width="25.61328125" customWidth="1"/>
-    <col min="3" max="3" width="30.69140625" customWidth="1"/>
+    <col min="1" max="1" width="26.7265625" customWidth="1"/>
+    <col min="2" max="2" width="25.6328125" customWidth="1"/>
+    <col min="3" max="3" width="30.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -828,7 +885,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -839,7 +896,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -850,7 +907,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -861,7 +918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -872,7 +929,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -883,7 +940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -900,16 +957,209 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6741521C-E770-4C8A-9A6D-530F4E09EB30}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="39.08984375" customWidth="1"/>
+    <col min="3" max="3" width="47.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9F8AE2F-1341-4921-A982-0ECB7367B1F7}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="28.1796875" customWidth="1"/>
+    <col min="3" max="3" width="40.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC3FD18-621C-4EB5-A9A2-608B2593CE23}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.07421875" customWidth="1"/>
-    <col min="2" max="2" width="24.23046875" customWidth="1"/>
-    <col min="3" max="3" width="27.3828125" customWidth="1"/>
+    <col min="1" max="1" width="27.08984375" customWidth="1"/>
+    <col min="2" max="2" width="24.26953125" customWidth="1"/>
+    <col min="3" max="3" width="27.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -920,7 +1170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -931,7 +1181,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -942,7 +1192,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -953,7 +1203,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -964,7 +1214,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Errors.xlsx
+++ b/src/main/resources/Errors.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Automation_Product\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13D902B-9B21-45BE-97F0-876BF4EB9E07}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB85B3C-2580-4ED6-B1C3-4DC8BB4AA202}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="3" activeTab="6" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="5" activeTab="5" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
   </bookViews>
   <sheets>
     <sheet name="AnnualError" sheetId="2" r:id="rId1"/>
@@ -19,8 +19,7 @@
     <sheet name="SemiAnnuallyError" sheetId="5" r:id="rId4"/>
     <sheet name="Bi-MonthlyForEightRecord" sheetId="7" r:id="rId5"/>
     <sheet name="Grant_Creation _Error" sheetId="8" r:id="rId6"/>
-    <sheet name="Grant_Creation _Error2" sheetId="9" r:id="rId7"/>
-    <sheet name="NoScheduleStartDateError" sheetId="6" r:id="rId8"/>
+    <sheet name="NoScheduleStartDateError" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,6 +29,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="31">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -130,9 +130,6 @@
   </si>
   <si>
     <t>Test Automation Organization</t>
-  </si>
-  <si>
-    <t>ProjectPeriodStartDate__c</t>
   </si>
 </sst>
 </file>
@@ -1059,97 +1056,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9F8AE2F-1341-4921-A982-0ECB7367B1F7}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="28.1796875" customWidth="1"/>
-    <col min="3" max="3" width="40.36328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC3FD18-621C-4EB5-A9A2-608B2593CE23}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/src/main/resources/Errors.xlsx
+++ b/src/main/resources/Errors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Automation_Product\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB85B3C-2580-4ED6-B1C3-4DC8BB4AA202}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35A5A15-4796-45B6-AF9D-EE7E31251FA4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="5" activeTab="5" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
   </bookViews>
   <sheets>
     <sheet name="AnnualError" sheetId="2" r:id="rId1"/>
@@ -495,14 +495,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A3F775-4EF9-4E52-8B04-750C37159D13}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.7265625" customWidth="1"/>
-    <col min="2" max="2" width="21.08984375" customWidth="1"/>
-    <col min="3" max="3" width="27.81640625" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -513,7 +513,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -524,7 +524,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -535,7 +535,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -546,7 +546,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -557,7 +557,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -568,7 +568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -587,14 +587,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E04EE11-11AC-4EDB-8021-AA7ECF589184}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6328125" customWidth="1"/>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="24.7265625" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -605,7 +605,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -616,7 +616,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -627,7 +627,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -638,7 +638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -649,7 +649,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -660,7 +660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -668,7 +668,7 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>59</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -679,14 +679,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD01CD2B-7253-4FAA-9A4D-E901801ECEA6}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6328125" customWidth="1"/>
-    <col min="2" max="2" width="21.36328125" customWidth="1"/>
-    <col min="3" max="3" width="22.453125" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -697,7 +697,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -708,7 +708,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -719,7 +719,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -730,7 +730,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -741,7 +741,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -752,7 +752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -771,14 +771,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{217E2F9E-9199-408F-BE46-44297F0B7560}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.54296875" customWidth="1"/>
-    <col min="2" max="2" width="18.36328125" customWidth="1"/>
-    <col min="3" max="3" width="31.7265625" customWidth="1"/>
+    <col min="1" max="1" width="29.5703125" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="31.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -789,7 +789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -800,7 +800,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -811,7 +811,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -822,7 +822,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -833,7 +833,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -844,7 +844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -864,14 +864,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71D36EAF-2C5D-489B-9FA4-63FF8286B375}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.7265625" customWidth="1"/>
-    <col min="2" max="2" width="25.6328125" customWidth="1"/>
-    <col min="3" max="3" width="30.7265625" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -882,7 +882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -893,7 +893,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -904,7 +904,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -915,7 +915,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -926,7 +926,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -956,13 +956,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6741521C-E770-4C8A-9A6D-530F4E09EB30}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="39.08984375" customWidth="1"/>
-    <col min="3" max="3" width="47.08984375" customWidth="1"/>
+    <col min="2" max="2" width="39.140625" customWidth="1"/>
+    <col min="3" max="3" width="47.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -973,7 +973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -984,7 +984,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -995,7 +995,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1058,14 +1058,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC3FD18-621C-4EB5-A9A2-608B2593CE23}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.08984375" customWidth="1"/>
-    <col min="2" max="2" width="24.26953125" customWidth="1"/>
-    <col min="3" max="3" width="27.36328125" customWidth="1"/>
+    <col min="1" max="1" width="27.140625" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Errors.xlsx
+++ b/src/main/resources/Errors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35A5A15-4796-45B6-AF9D-EE7E31251FA4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B2C4B3-72BF-41A9-9695-E8B94C6C6916}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" firstSheet="4" activeTab="6" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
   </bookViews>
   <sheets>
     <sheet name="AnnualError" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="32">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -130,6 +130,9 @@
   </si>
   <si>
     <t>Test Automation Organization</t>
+  </si>
+  <si>
+    <t>fieldFrequency__c</t>
   </si>
 </sst>
 </file>
@@ -495,14 +498,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A3F775-4EF9-4E52-8B04-750C37159D13}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" customWidth="1"/>
-    <col min="3" max="3" width="27.85546875" customWidth="1"/>
+    <col min="1" max="1" width="17.73046875" customWidth="1"/>
+    <col min="2" max="2" width="21.1328125" customWidth="1"/>
+    <col min="3" max="3" width="27.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -513,7 +516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -524,7 +527,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -535,7 +538,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -546,7 +549,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -557,7 +560,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -568,7 +571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -587,14 +590,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E04EE11-11AC-4EDB-8021-AA7ECF589184}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" customWidth="1"/>
+    <col min="1" max="1" width="20.59765625" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -605,7 +608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -616,7 +619,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -627,7 +630,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -638,7 +641,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -649,7 +652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -660,7 +663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -679,14 +682,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD01CD2B-7253-4FAA-9A4D-E901801ECEA6}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" customWidth="1"/>
+    <col min="1" max="1" width="18.59765625" customWidth="1"/>
+    <col min="2" max="2" width="21.3984375" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -697,7 +700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -708,7 +711,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -719,7 +722,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -730,7 +733,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -741,7 +744,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -752,7 +755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -771,14 +774,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{217E2F9E-9199-408F-BE46-44297F0B7560}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.5703125" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="31.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.59765625" customWidth="1"/>
+    <col min="2" max="2" width="18.3984375" customWidth="1"/>
+    <col min="3" max="3" width="31.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -789,7 +792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -800,18 +803,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -822,7 +825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -833,7 +836,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -844,7 +847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -864,14 +867,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71D36EAF-2C5D-489B-9FA4-63FF8286B375}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="26.73046875" customWidth="1"/>
+    <col min="2" max="2" width="25.59765625" customWidth="1"/>
+    <col min="3" max="3" width="30.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -882,7 +885,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -893,7 +896,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -904,7 +907,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -915,7 +918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -926,7 +929,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -937,7 +940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -956,13 +959,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6741521C-E770-4C8A-9A6D-530F4E09EB30}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="39.140625" customWidth="1"/>
-    <col min="3" max="3" width="47.140625" customWidth="1"/>
+    <col min="2" max="2" width="39.1328125" customWidth="1"/>
+    <col min="3" max="3" width="47.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -973,7 +976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -984,7 +987,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -995,7 +998,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1006,7 +1009,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1017,7 +1020,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1028,7 +1031,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1039,7 +1042,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1058,14 +1061,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC3FD18-621C-4EB5-A9A2-608B2593CE23}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="27.140625" customWidth="1"/>
-    <col min="2" max="2" width="24.28515625" customWidth="1"/>
-    <col min="3" max="3" width="27.42578125" customWidth="1"/>
+    <col min="1" max="1" width="27.1328125" customWidth="1"/>
+    <col min="2" max="2" width="24.265625" customWidth="1"/>
+    <col min="3" max="3" width="27.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1076,7 +1079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1087,18 +1090,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1109,7 +1112,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1120,7 +1123,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Errors.xlsx
+++ b/src/main/resources/Errors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23901"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B2C4B3-72BF-41A9-9695-E8B94C6C6916}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82CFF48-CCF5-450E-911D-5AC8C37B6624}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" firstSheet="4" activeTab="6" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" firstSheet="1" activeTab="2" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
   </bookViews>
   <sheets>
     <sheet name="AnnualError" sheetId="2" r:id="rId1"/>
@@ -763,7 +763,7 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Errors.xlsx
+++ b/src/main/resources/Errors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82CFF48-CCF5-450E-911D-5AC8C37B6624}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8061E6F3-56B9-4E7E-A27C-CA8DC7B41273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" firstSheet="1" activeTab="2" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
+    <workbookView xWindow="210" yWindow="0" windowWidth="20355" windowHeight="10920" firstSheet="1" activeTab="1" xr2:uid="{1723DB62-37ED-4AF2-A84E-95702473D7B6}"/>
   </bookViews>
   <sheets>
     <sheet name="AnnualError" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="37">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -133,13 +133,28 @@
   </si>
   <si>
     <t>fieldFrequency__c</t>
+  </si>
+  <si>
+    <t>fieldCalReportingStartDate__c</t>
+  </si>
+  <si>
+    <t>fieldCalReportingEndDate__c</t>
+  </si>
+  <si>
+    <t>fieldSubmissionTitle__c</t>
+  </si>
+  <si>
+    <t>fieldScheduleBase__c</t>
+  </si>
+  <si>
+    <t>fieldDescription__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,6 +165,12 @@
     <font>
       <sz val="9"/>
       <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF202124"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -174,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -183,6 +204,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -498,14 +520,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A3F775-4EF9-4E52-8B04-750C37159D13}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.73046875" customWidth="1"/>
-    <col min="2" max="2" width="21.1328125" customWidth="1"/>
-    <col min="3" max="3" width="27.86328125" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -516,7 +538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -527,7 +549,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -538,7 +560,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -549,7 +571,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -560,7 +582,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -571,7 +593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -590,14 +612,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E04EE11-11AC-4EDB-8021-AA7ECF589184}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.59765625" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="24.73046875" customWidth="1"/>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -608,67 +630,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
+      <c r="B2" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
+      <c r="B3" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
+      <c r="B4" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>11</v>
+      <c r="B5" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>12</v>
+      <c r="B6" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" t="s">
-        <v>13</v>
+      <c r="B7" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="C7">
         <v>20</v>
@@ -682,14 +704,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD01CD2B-7253-4FAA-9A4D-E901801ECEA6}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.59765625" customWidth="1"/>
-    <col min="2" max="2" width="21.3984375" customWidth="1"/>
-    <col min="3" max="3" width="22.3984375" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -700,7 +722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -711,7 +733,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -722,7 +744,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -733,7 +755,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -744,7 +766,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -755,7 +777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -774,14 +796,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{217E2F9E-9199-408F-BE46-44297F0B7560}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.3984375" customWidth="1"/>
-    <col min="3" max="3" width="31.73046875" customWidth="1"/>
+    <col min="1" max="1" width="29.5703125" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -792,67 +814,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
+      <c r="B2" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
+      <c r="B4" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>11</v>
+      <c r="B5" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>12</v>
+      <c r="B6" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" t="s">
-        <v>13</v>
+      <c r="B7" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -867,14 +889,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71D36EAF-2C5D-489B-9FA4-63FF8286B375}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.73046875" customWidth="1"/>
-    <col min="2" max="2" width="25.59765625" customWidth="1"/>
-    <col min="3" max="3" width="30.73046875" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -885,7 +907,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -896,7 +918,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -907,7 +929,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -918,7 +940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -929,7 +951,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -940,7 +962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -959,13 +981,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6741521C-E770-4C8A-9A6D-530F4E09EB30}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="39.1328125" customWidth="1"/>
-    <col min="3" max="3" width="47.1328125" customWidth="1"/>
+    <col min="2" max="2" width="39.140625" customWidth="1"/>
+    <col min="3" max="3" width="47.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -976,7 +998,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -987,7 +1009,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -998,7 +1020,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1009,7 +1031,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1020,7 +1042,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1031,7 +1053,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1042,7 +1064,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1061,14 +1083,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC3FD18-621C-4EB5-A9A2-608B2593CE23}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.265625" customWidth="1"/>
-    <col min="3" max="3" width="27.3984375" customWidth="1"/>
+    <col min="1" max="1" width="27.140625" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1079,7 +1101,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1090,7 +1112,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1101,7 +1123,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1112,7 +1134,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1123,7 +1145,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
